--- a/www/flightdata/xlsx/eoss-379.xlsx
+++ b/www/flightdata/xlsx/eoss-379.xlsx
@@ -4245,7 +4245,7 @@
         <v>29527.2</v>
       </c>
       <c r="I2">
-        <v>896</v>
+        <v>571</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
